--- a/hardware/components.xlsx
+++ b/hardware/components.xlsx
@@ -8,8 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Verification" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Stock" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -21,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="617">
   <si>
     <t xml:space="preserve">Function</t>
   </si>
@@ -188,7 +187,7 @@
     <t xml:space="preserve">C239251</t>
   </si>
   <si>
-    <t xml:space="preserve">Device:C_Polarized</t>
+    <t xml:space="preserve">Device:C_Polarized_Small</t>
   </si>
   <si>
     <t xml:space="preserve">Capacitor_SMD:CP_Elec_16x17.5</t>
@@ -239,7 +238,7 @@
     <t xml:space="preserve">C110255</t>
   </si>
   <si>
-    <t xml:space="preserve">Device:C</t>
+    <t xml:space="preserve">Device:C_Small</t>
   </si>
   <si>
     <t xml:space="preserve">Capacitor_SMD:C_1206_3216Metric</t>
@@ -647,6 +646,69 @@
     <t xml:space="preserve">https://www.lcsc.com/datasheet/C142852.pdf</t>
   </si>
   <si>
+    <t xml:space="preserve">Header</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54-1*20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Through Hole, P=2.54mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C5156618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connector_Generic:Conn_01x20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connector_PinHeader_2.54mm:PinHeader_1x20_P2.54mm_Vertical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-position, single-row, 2.54 mm-pitch pin header</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.lcsc.com/datasheet/C5156618.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PM254V-11-04-H85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Through Hole,P=2.54mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C541851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connector:Conn_01x04_Female</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connector_PinSocket_2.54mm:PinSocket_1x04_P2.54mm_Vertical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3A 4P -40℃~+105℃ Through Hole 8.5mm 1x4P Top 2.54mm 1 Square Hole Through Hole,P=2.54mm Headers, Receptacles, Female Sockets </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.lcsc.com/datasheet/C541851.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PZ254V-11-04P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2691448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connector:Conn_01x04_Pin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connector_PinHeader_2.54mm:PinHeader_1x04_P2.54mm_Vertical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pin Header 4 Position 2.54mm Pitch Single Row Through Hole -40℃~+105℃</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.lcsc.com/datasheet/C2691448.pdf</t>
+  </si>
+  <si>
     <t xml:space="preserve">Indicator LED</t>
   </si>
   <si>
@@ -836,30 +898,6 @@
     <t xml:space="preserve">https://www.lcsc.com/datasheet/C155176.pdf</t>
   </si>
   <si>
-    <t xml:space="preserve">Male Header Connector</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54-1*20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Through Hole, P=2.54mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C5156618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connector_Generic:Conn_01x20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connector_PinHeader_2.54mm:PinHeader_1x20_P2.54mm_Vertical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-position, single-row, 2.54 mm-pitch pin header</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/datasheet/C5156618.pdf</t>
-  </si>
-  <si>
     <t xml:space="preserve">Microcontroller</t>
   </si>
   <si>
@@ -1619,9 +1657,6 @@
     <t xml:space="preserve">TY308-2.54-02P-14-00AH</t>
   </si>
   <si>
-    <t xml:space="preserve">Through Hole,P=2.54mm</t>
-  </si>
-  <si>
     <t xml:space="preserve">C2840316</t>
   </si>
   <si>
@@ -1682,7 +1717,7 @@
     <t xml:space="preserve">Transistor</t>
   </si>
   <si>
-    <t xml:space="preserve">MMBT3904</t>
+    <t xml:space="preserve">MMBT3904 (NPN)</t>
   </si>
   <si>
     <t xml:space="preserve">C20526</t>
@@ -1697,7 +1732,7 @@
     <t xml:space="preserve">https://www.lcsc.com/datasheet/C20526.pdf</t>
   </si>
   <si>
-    <t xml:space="preserve">MMBT3906</t>
+    <t xml:space="preserve">MMBT3906 (PNP)</t>
   </si>
   <si>
     <t xml:space="preserve">C2143</t>
@@ -1836,372 +1871,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.lcsc.com/datasheet/C20612462.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verification &amp; reconciliation notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Original master stock + receipts from orders WM2610270663 and WM2610290613; historic orders already reflected in stock and not counted twice.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stock timing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final stock after delivery of the two newest orders, as requested.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCSC datasheets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only links whose LCSC datasheet viewer was verified for the code are populated. Blank means not confirmed, not proof the datasheet does not exist.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KiCad names</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only KiCad 10 library identifiers confirmed to exist, with match checked where possible. Empty values mean no reliable exact mapping; do not substitute blindly.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qty Set 1 / Set 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Existing stock allocations preserved; newly received units booked as separate stock set when possible.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Previously blank quantities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No historic purchases have been converted into assumed current stock when master stock was blank.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-LCSC stock-only parts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preserved even when missing from supplied historic order CSVs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Updated unique LCSC SKUs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New SKUs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New receipts (pieces)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verified LCSC datasheet links</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KiCad symbols populated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KiCad footprints populated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entries with some unverified enrichment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check / correction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Details</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New SKU, latest order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Added stock of 300 units from ABS210.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verified correction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Updated from ('SRRS75M2F', 'SOIC-8', 'STLM75 I2C/SMBus digital temperature sensor and thermal watchdog, -55 °C to +125 °C, ±2 °C') to ('STLM75M2F', 'SOIC-8', 'STLM75 I2C/SMBus digital temperature sensor and thermal watchdog, -55 °C to +125 °C, ±2 °C'); source: ordered manufacturer part and/or LCSC specifications.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Added stock of 20 units from 0452002.MRL.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Updated from ('AO3401A', 'SOT-323', 'P-channel MOSFET, -30 V, -4 A') to ('AO3401A', 'SOT-23', 'P-channel MOSFET, -30 V, -4 A'); source: ordered manufacturer part and/or LCSC specifications.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C17901 / C118845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corrected composite SKU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Split 1000 pcs at C17901 (1% tolerance) and 1000 pcs at C118845 (5%) based on separate ordered line items and existing Set 1 / Set 2 stock.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Added stock of 1000 units from 24C02S(XBLW).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Added stock of 60 units from 1210B475K101NT.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latest order received</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Added 300 units; previous total 1000, final total 1300.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manufacturer part text differs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Earlier order says XL-5050RGBC-WS2812B; latest order says XL-5050RGBC-2812B for the same LCSC C2843785. Current SKU kept as latest order name. Confirm pin orientation against the exact batch before PCB design.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pinout matched</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XINGLIGHT datasheet pin numbers 1=VDD, 2=DO, 3=GND, 4=DI match KiCad WS2812B library pad numbering.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Updated from ('WS2812B', '5050', 'WS2812B-compatible individually addressable RGB LED with integrated driver') to ('XL-5050RGBC-2812B', 'SMD5050-4P', 'WS2812B-compatible individually addressable RGB LED with integrated driver'); source: ordered manufacturer part and/or LCSC specifications.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Updated from ('Yellow', '5050', 'White indicator LED, 3.4 V, six leads') to ('White (yellow lens)', 'SMD5050-6P', 'White indicator LED, six leads, yellow-coloured lens'); source: ordered manufacturer part and/or LCSC specifications.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Updated from ('FRC0603F1802TS', 603, '18kΩ ±1% 100mW 0603 Thick Film Resistor') to ('FRC0603F1802TS', '0603', '18kΩ ±1% 100mW 0603 Thick Film Resistor'); source: ordered manufacturer part and/or LCSC specifications.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Added stock of 100 units from FRC1206F3600TS.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Updated from ('LM2576S-12', 'TO-263', 'Fixed 12 V, 3 A step-down switching regulator') to ('LM2576S-12', 'TO-263-5', 'Fixed 12 V, 3 A step-down switching regulator'); source: ordered manufacturer part and/or LCSC specifications.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Updated from ('USM1', 'SMA', '1 kV, 1 A fast-recovery rectifier, 75 ns') to ('US1M', 'SMA', '1 kV, 1 A fast-recovery rectifier, 75 ns'); source: ordered manufacturer part and/or LCSC specifications.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Added stock of 2 units from SN65HVD72DR.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Updated from ('CL0603FN4K3P', 603, '4.3kΩ ±1% 100mW 0603 Thick Film Resistor') to ('CL0603FN4K3P', '0603', '4.3kΩ ±1% 100mW 0603 Thick Film Resistor'); source: ordered manufacturer part and/or LCSC specifications.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Added stock of 100 units from FCC0603N180J500CT.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Removed duplicate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two identical 100-piece LMR38020 rows in master; only one 100-piece order exists, so kept one row with 100 total.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Added stock of 100 units from 3225 24M 12PF 10PPM.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Added 200 units; previous total 10, final total 210.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Added 50 units; previous total 40, final total 90.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Updated from ('1000u', 'D16x26mm', '63V ±20% 1000uF 54mΩ@100kHz Through Hole,D16xL26mm Aluminum Electrolytic Capacitors RoHS') to ('1000u', 'THT D16xL26mm P7.5mm', '63V ±20% 1000uF 54mΩ@100kHz Through Hole,D16xL26mm Aluminum Electrolytic Capacitors RoHS'); source: ordered manufacturer part and/or LCSC specifications.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Updated from ('Green', '0805', 'Ice-blue indicator LED, 3.3 V') to ('Ice Blue', '0805', 'Ice-blue indicator LED, 3.3 V'); source: ordered manufacturer part and/or LCSC specifications.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unverified / requires exact matching</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCSC product page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCSC datasheet link unverified, exact KiCad symbol unverified, matching KiCad footprint unverified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C6969504.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exact KiCad symbol unverified, matching KiCad footprint unverified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C123897.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C5149193.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">matching KiCad footprint unverified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C239251.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C3445233.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C46638858.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C4747972.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCSC datasheet link unverified, matching KiCad footprint unverified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C700860.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C4747974.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C4747978.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C2894225.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exact KiCad symbol unverified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C5181479.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C139728.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C18723540.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C18723066.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C2935888.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C142852.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C2843867.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C128802.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C278365.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCSC datasheet link unverified, exact KiCad symbol unverified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C7473143.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C5156618.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C5187096.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C5299908.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C5148642.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C15127.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C32565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C32565.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C5300004.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C499607.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C26858.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C636429.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCSC datasheet link unverified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C2907418.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C18004.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C2930362.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C163892.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C2907474.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C2933675.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C2933683.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C3013388.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C48391830.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C269612.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C48125.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C6855.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C97521.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C318884.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C557685.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C2840316.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C2840317.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C2840318.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C2928791.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C2831691.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C2764612.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C46043.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C177019.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C20612462.html</t>
   </si>
 </sst>
 </file>
@@ -2257,6 +1926,11 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
@@ -2274,16 +1948,8 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF193C43"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2293,13 +1959,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF214E56"/>
-        <bgColor rgb="FF193C43"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2E5E9"/>
-        <bgColor rgb="FFCCFFFF"/>
+        <bgColor rgb="FF15628C"/>
       </patternFill>
     </fill>
   </fills>
@@ -2341,7 +2001,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2374,19 +2034,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2466,7 +2122,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF15628C"/>
-      <rgbColor rgb="FFD2E5E9"/>
+      <rgbColor rgb="FFCCCCFF"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -2491,14 +2147,14 @@
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF214E56"/>
+      <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF193C43"/>
+      <rgbColor rgb="FF214E56"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -2874,7 +2530,7 @@
       <c r="D7" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="6" t="s">
         <v>55</v>
       </c>
       <c r="F7" s="1" t="s">
@@ -2909,7 +2565,7 @@
       <c r="D8" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="6" t="s">
         <v>55</v>
       </c>
       <c r="F8" s="1" t="s">
@@ -2944,7 +2600,7 @@
       <c r="D9" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="6" t="s">
         <v>55</v>
       </c>
       <c r="F9" s="1" t="s">
@@ -3156,10 +2812,10 @@
       <c r="D15" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="7" t="s">
         <v>99</v>
       </c>
       <c r="G15" s="4" t="n">
@@ -3189,7 +2845,7 @@
       <c r="D16" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="6" t="s">
         <v>55</v>
       </c>
       <c r="F16" s="1" t="s">
@@ -3224,7 +2880,7 @@
       <c r="D17" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="6" t="s">
         <v>55</v>
       </c>
       <c r="F17" s="1" t="s">
@@ -3292,7 +2948,7 @@
       <c r="D19" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="6" t="s">
         <v>55</v>
       </c>
       <c r="F19" s="1" t="s">
@@ -3362,7 +3018,7 @@
       <c r="D21" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="8" t="s">
         <v>130</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -3469,7 +3125,7 @@
       <c r="D24" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="8" t="s">
         <v>153</v>
       </c>
       <c r="F24" s="1" t="s">
@@ -3755,14 +3411,12 @@
       </c>
       <c r="G32" s="4" t="n">
         <f aca="false">SUM(H32:J32)</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>500</v>
-      </c>
-      <c r="I32" s="4" t="n">
-        <v>500</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I32" s="4"/>
       <c r="J32" s="4"/>
       <c r="K32" s="1" t="s">
         <v>214</v>
@@ -3775,180 +3429,178 @@
       <c r="A33" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D33" s="3" t="s">
+      <c r="C33" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>212</v>
+      <c r="D33" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>219</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="G33" s="4" t="n">
         <f aca="false">SUM(H33:J33)</f>
-        <v>500</v>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>500</v>
-      </c>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="L33" s="5" t="s">
-        <v>219</v>
+        <v>1000</v>
+      </c>
+      <c r="H33" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="L33" s="10" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>221</v>
+      <c r="B34" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>224</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="G34" s="4" t="n">
         <f aca="false">SUM(H34:J34)</f>
-        <v>500</v>
-      </c>
-      <c r="H34" s="4" t="n">
-        <v>500</v>
-      </c>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="L34" s="5" t="s">
-        <v>223</v>
+        <v>1000</v>
+      </c>
+      <c r="H34" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="L34" s="10" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="G35" s="4" t="n">
         <f aca="false">SUM(H35:J35)</f>
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="I35" s="4"/>
+        <v>500</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>500</v>
+      </c>
       <c r="J35" s="4"/>
       <c r="K35" s="1" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="L35" s="5" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="D36" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="F36" s="1" t="s">
         <v>234</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>235</v>
       </c>
       <c r="G36" s="4" t="n">
         <f aca="false">SUM(H36:J36)</f>
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
       <c r="K36" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="L36" s="5" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>239</v>
-      </c>
       <c r="D37" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E37" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>234</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>241</v>
       </c>
       <c r="G37" s="4" t="n">
         <f aca="false">SUM(H37:J37)</f>
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="I37" s="4"/>
       <c r="J37" s="4"/>
       <c r="K37" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L37" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>245</v>
@@ -3967,10 +3619,10 @@
       </c>
       <c r="G38" s="4" t="n">
         <f aca="false">SUM(H38:J38)</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
@@ -3983,92 +3635,92 @@
     </row>
     <row r="39" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>246</v>
+        <v>70</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="G39" s="4" t="n">
         <f aca="false">SUM(H39:J39)</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
       <c r="K39" s="1" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="L39" s="5" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="D40" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>256</v>
-      </c>
       <c r="F40" s="1" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="G40" s="4" t="n">
         <f aca="false">SUM(H40:J40)</f>
-        <v>104</v>
+        <v>50</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>104</v>
+        <v>50</v>
       </c>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
       <c r="K40" s="1" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="L40" s="5" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>256</v>
+        <v>268</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>269</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="G41" s="4" t="n">
         <f aca="false">SUM(H41:J41)</f>
@@ -4080,273 +3732,273 @@
       <c r="I41" s="4"/>
       <c r="J41" s="4"/>
       <c r="K41" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="L41" s="5"/>
+        <v>271</v>
+      </c>
+      <c r="L41" s="5" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="G42" s="4" t="n">
         <f aca="false">SUM(H42:J42)</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
       <c r="K42" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L42" s="5" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="G43" s="4" t="n">
         <f aca="false">SUM(H43:J43)</f>
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
       <c r="K43" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L43" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="B44" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="D44" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="E44" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="F44" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>284</v>
       </c>
       <c r="G44" s="4" t="n">
         <f aca="false">SUM(H44:J44)</f>
-        <v>210</v>
+        <v>300</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="I44" s="4" t="n">
-        <v>200</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="I44" s="4"/>
       <c r="J44" s="4"/>
       <c r="K44" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="L44" s="5" t="s">
-        <v>286</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="L44" s="5"/>
     </row>
     <row r="45" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="E45" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="F45" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>291</v>
       </c>
       <c r="G45" s="4" t="n">
         <f aca="false">SUM(H45:J45)</f>
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
       <c r="K45" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="L45" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="D46" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="E46" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="F46" s="1" t="s">
         <v>297</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>299</v>
       </c>
       <c r="G46" s="4" t="n">
         <f aca="false">SUM(H46:J46)</f>
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I46" s="4"/>
+        <v>10</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>200</v>
+      </c>
       <c r="J46" s="4"/>
       <c r="K46" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="L46" s="5"/>
+        <v>298</v>
+      </c>
+      <c r="L46" s="5" t="s">
+        <v>299</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="D47" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="E47" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="F47" s="1" t="s">
         <v>304</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>177</v>
       </c>
       <c r="G47" s="4" t="n">
         <f aca="false">SUM(H47:J47)</f>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
       <c r="K47" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="L47" s="5" t="s">
         <v>306</v>
-      </c>
-      <c r="L47" s="5" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="C48" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="D48" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="E48" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="E48" s="7" t="s">
+      <c r="F48" s="1" t="s">
         <v>312</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>313</v>
       </c>
       <c r="G48" s="4" t="n">
         <f aca="false">SUM(H48:J48)</f>
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
       <c r="K48" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="L48" s="5" t="s">
-        <v>315</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="L48" s="5"/>
     </row>
     <row r="49" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="D49" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="E49" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>321</v>
+      <c r="F49" s="1" t="s">
+        <v>177</v>
       </c>
       <c r="G49" s="4" t="n">
         <f aca="false">SUM(H49:J49)</f>
@@ -4358,72 +4010,72 @@
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
       <c r="K49" s="1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="L49" s="5" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="D50" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="E50" s="8" t="s">
         <v>325</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D50" s="3" t="s">
+      <c r="F50" s="1" t="s">
         <v>326</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>313</v>
       </c>
       <c r="G50" s="4" t="n">
         <f aca="false">SUM(H50:J50)</f>
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
       <c r="K50" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="L50" s="5" t="s">
         <v>328</v>
-      </c>
-      <c r="L50" s="5" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="C51" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="D51" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="E51" s="8" t="s">
         <v>333</v>
       </c>
-      <c r="E51" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="F51" s="1" t="s">
+      <c r="F51" s="8" t="s">
         <v>334</v>
       </c>
       <c r="G51" s="4" t="n">
         <f aca="false">SUM(H51:J51)</f>
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="I51" s="4"/>
       <c r="J51" s="4"/>
@@ -4442,58 +4094,58 @@
         <v>338</v>
       </c>
       <c r="C52" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="E52" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>341</v>
-      </c>
       <c r="F52" s="1" t="s">
-        <v>268</v>
+        <v>326</v>
       </c>
       <c r="G52" s="4" t="n">
         <f aca="false">SUM(H52:J52)</f>
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
       <c r="K52" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L52" s="5" t="s">
         <v>342</v>
-      </c>
-      <c r="L52" s="5" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="C53" s="1" t="s">
         <v>345</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>265</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>346</v>
       </c>
       <c r="E53" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="F53" s="1" t="s">
         <v>347</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>268</v>
       </c>
       <c r="G53" s="4" t="n">
         <f aca="false">SUM(H53:J53)</f>
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
@@ -4521,143 +4173,143 @@
         <v>354</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>154</v>
+        <v>289</v>
       </c>
       <c r="G54" s="4" t="n">
         <f aca="false">SUM(H54:J54)</f>
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="I54" s="4"/>
       <c r="J54" s="4"/>
       <c r="K54" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="L54" s="5"/>
+      <c r="L54" s="5" t="s">
+        <v>356</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>357</v>
+        <v>286</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>360</v>
+        <v>289</v>
       </c>
       <c r="G55" s="4" t="n">
         <f aca="false">SUM(H55:J55)</f>
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="I55" s="4"/>
       <c r="J55" s="4"/>
       <c r="K55" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="L55" s="5"/>
+      <c r="L55" s="5" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>70</v>
+        <v>365</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>366</v>
+        <v>154</v>
       </c>
       <c r="G56" s="4" t="n">
         <f aca="false">SUM(H56:J56)</f>
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="I56" s="4"/>
       <c r="J56" s="4"/>
       <c r="K56" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="L56" s="5" t="s">
         <v>368</v>
       </c>
+      <c r="L56" s="5"/>
     </row>
     <row r="57" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>369</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>70</v>
+        <v>370</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="G57" s="4" t="n">
         <f aca="false">SUM(H57:J57)</f>
-        <v>1000</v>
+        <v>2</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>1000</v>
+        <v>2</v>
       </c>
       <c r="I57" s="4"/>
       <c r="J57" s="4"/>
       <c r="K57" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="L57" s="5" t="s">
-        <v>372</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="L57" s="5"/>
     </row>
     <row r="58" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>70</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="G58" s="4" t="n">
         <f aca="false">SUM(H58:J58)</f>
@@ -4669,63 +4321,65 @@
       <c r="I58" s="4"/>
       <c r="J58" s="4"/>
       <c r="K58" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="L58" s="5"/>
+        <v>380</v>
+      </c>
+      <c r="L58" s="5" t="s">
+        <v>381</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G59" s="4" t="n">
         <f aca="false">SUM(H59:J59)</f>
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="I59" s="4"/>
       <c r="J59" s="4"/>
       <c r="K59" s="1" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="L59" s="5" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>70</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="G60" s="4" t="n">
         <f aca="false">SUM(H60:J60)</f>
@@ -4737,308 +4391,304 @@
       <c r="I60" s="4"/>
       <c r="J60" s="4"/>
       <c r="K60" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="L60" s="5" t="s">
-        <v>384</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="L60" s="5"/>
     </row>
     <row r="61" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>366</v>
+        <v>391</v>
       </c>
       <c r="G61" s="4" t="n">
         <f aca="false">SUM(H61:J61)</f>
-        <v>1000</v>
-      </c>
-      <c r="H61" s="4"/>
-      <c r="I61" s="4" t="n">
-        <v>1000</v>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="H61" s="4" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I61" s="4"/>
       <c r="J61" s="4"/>
       <c r="K61" s="1" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="L61" s="5" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>70</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="G62" s="4" t="n">
         <f aca="false">SUM(H62:J62)</f>
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="I62" s="4"/>
       <c r="J62" s="4"/>
       <c r="K62" s="1" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="L62" s="5" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="C63" s="1" t="n">
-        <v>1206</v>
+        <v>398</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="G63" s="4" t="n">
         <f aca="false">SUM(H63:J63)</f>
         <v>1000</v>
       </c>
-      <c r="H63" s="4" t="n">
+      <c r="H63" s="4"/>
+      <c r="I63" s="4" t="n">
         <v>1000</v>
       </c>
-      <c r="I63" s="4"/>
       <c r="J63" s="4"/>
       <c r="K63" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="L63" s="5"/>
+        <v>400</v>
+      </c>
+      <c r="L63" s="5" t="s">
+        <v>401</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>70</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="G64" s="4" t="n">
         <f aca="false">SUM(H64:J64)</f>
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="I64" s="4"/>
       <c r="J64" s="4"/>
       <c r="K64" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="L64" s="5" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>70</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="G65" s="4" t="n">
         <f aca="false">SUM(H65:J65)</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I65" s="4"/>
       <c r="J65" s="4"/>
       <c r="K65" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="L65" s="5" t="s">
-        <v>403</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="L65" s="5"/>
     </row>
     <row r="66" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="B66" s="8" t="s">
-        <v>404</v>
+        <v>375</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>409</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D66" s="8" t="s">
-        <v>405</v>
-      </c>
-      <c r="E66" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="F66" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>378</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>379</v>
       </c>
       <c r="G66" s="4" t="n">
         <f aca="false">SUM(H66:J66)</f>
-        <v>2000</v>
-      </c>
-      <c r="H66" s="1" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K66" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="L66" s="9" t="s">
-        <v>407</v>
+        <v>1000</v>
+      </c>
+      <c r="H66" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="L66" s="5" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>70</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="G67" s="4" t="n">
         <f aca="false">SUM(H67:J67)</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I67" s="4"/>
       <c r="J67" s="4"/>
       <c r="K67" s="1" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="L67" s="5" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>412</v>
+        <v>375</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>417</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="F68" s="1" t="s">
+      <c r="D68" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="E68" s="9" t="s">
         <v>378</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>391</v>
       </c>
       <c r="G68" s="4" t="n">
         <f aca="false">SUM(H68:J68)</f>
-        <v>2100</v>
-      </c>
-      <c r="H68" s="4" t="n">
         <v>2000</v>
       </c>
-      <c r="I68" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="J68" s="4"/>
-      <c r="K68" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="L68" s="5" t="s">
-        <v>415</v>
+      <c r="H68" s="1" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K68" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="L68" s="10" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>70</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="G69" s="4" t="n">
         <f aca="false">SUM(H69:J69)</f>
@@ -5050,61 +4700,67 @@
       <c r="I69" s="4"/>
       <c r="J69" s="4"/>
       <c r="K69" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="L69" s="5"/>
+        <v>423</v>
+      </c>
+      <c r="L69" s="5" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="G70" s="4" t="n">
         <f aca="false">SUM(H70:J70)</f>
-        <v>1000</v>
+        <v>2100</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I70" s="4"/>
+        <v>2000</v>
+      </c>
+      <c r="I70" s="4" t="n">
+        <v>100</v>
+      </c>
       <c r="J70" s="4"/>
       <c r="K70" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="L70" s="5"/>
+        <v>427</v>
+      </c>
+      <c r="L70" s="5" t="s">
+        <v>428</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="C71" s="1" t="n">
-        <v>1206</v>
+        <v>429</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="G71" s="4" t="n">
         <f aca="false">SUM(H71:J71)</f>
@@ -5116,28 +4772,28 @@
       <c r="I71" s="4"/>
       <c r="J71" s="4"/>
       <c r="K71" s="1" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="L71" s="5"/>
     </row>
     <row r="72" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>366</v>
+        <v>391</v>
       </c>
       <c r="G72" s="4" t="n">
         <f aca="false">SUM(H72:J72)</f>
@@ -5149,61 +4805,61 @@
       <c r="I72" s="4"/>
       <c r="J72" s="4"/>
       <c r="K72" s="1" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="L72" s="5"/>
     </row>
     <row r="73" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>70</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="G73" s="4" t="n">
         <f aca="false">SUM(H73:J73)</f>
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="I73" s="4"/>
       <c r="J73" s="4"/>
       <c r="K73" s="1" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="L73" s="5"/>
     </row>
     <row r="74" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>70</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="G74" s="4" t="n">
         <f aca="false">SUM(H74:J74)</f>
@@ -5215,199 +4871,197 @@
       <c r="I74" s="4"/>
       <c r="J74" s="4"/>
       <c r="K74" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="L74" s="5" t="s">
-        <v>434</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="L74" s="5"/>
     </row>
     <row r="75" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G75" s="4" t="n">
         <f aca="false">SUM(H75:J75)</f>
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="I75" s="4"/>
       <c r="J75" s="4"/>
       <c r="K75" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="L75" s="5" t="s">
-        <v>437</v>
-      </c>
+        <v>443</v>
+      </c>
+      <c r="L75" s="5"/>
     </row>
     <row r="76" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="B76" s="8" t="s">
-        <v>438</v>
+        <v>375</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>444</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D76" s="8" t="s">
-        <v>439</v>
-      </c>
-      <c r="E76" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="F76" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="E76" s="1" t="s">
         <v>378</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>379</v>
       </c>
       <c r="G76" s="4" t="n">
         <f aca="false">SUM(H76:J76)</f>
-        <v>2000</v>
-      </c>
-      <c r="H76" s="1" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K76" s="8" t="s">
-        <v>440</v>
-      </c>
-      <c r="L76" s="1" t="s">
-        <v>441</v>
+        <v>1000</v>
+      </c>
+      <c r="H76" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="L76" s="5" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>443</v>
+        <v>76</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>445</v>
+        <v>391</v>
       </c>
       <c r="G77" s="4" t="n">
         <f aca="false">SUM(H77:J77)</f>
-        <v>100</v>
+        <v>2000</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>100</v>
+        <v>2000</v>
       </c>
       <c r="I77" s="4"/>
       <c r="J77" s="4"/>
       <c r="K77" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="L77" s="5"/>
+        <v>449</v>
+      </c>
+      <c r="L77" s="5" t="s">
+        <v>450</v>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>447</v>
+        <v>375</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>451</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>366</v>
+        <v>76</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="E78" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>391</v>
       </c>
       <c r="G78" s="4" t="n">
         <f aca="false">SUM(H78:J78)</f>
-        <v>1000</v>
-      </c>
-      <c r="H78" s="4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I78" s="4"/>
-      <c r="J78" s="4"/>
-      <c r="K78" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="L78" s="5" t="s">
-        <v>450</v>
+        <v>2000</v>
+      </c>
+      <c r="H78" s="1" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K78" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="L78" s="1" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>76</v>
+        <v>456</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>378</v>
+        <v>458</v>
       </c>
       <c r="G79" s="4" t="n">
         <f aca="false">SUM(H79:J79)</f>
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="I79" s="4"/>
       <c r="J79" s="4"/>
       <c r="K79" s="1" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="L79" s="5"/>
     </row>
     <row r="80" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G80" s="4" t="n">
         <f aca="false">SUM(H80:J80)</f>
@@ -5419,30 +5073,30 @@
       <c r="I80" s="4"/>
       <c r="J80" s="4"/>
       <c r="K80" s="1" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="L80" s="5" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="C81" s="1" t="n">
-        <v>1206</v>
+        <v>464</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>366</v>
+        <v>391</v>
       </c>
       <c r="G81" s="4" t="n">
         <f aca="false">SUM(H81:J81)</f>
@@ -5454,30 +5108,28 @@
       <c r="I81" s="4"/>
       <c r="J81" s="4"/>
       <c r="K81" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="L81" s="5" t="s">
-        <v>461</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="L81" s="5"/>
     </row>
     <row r="82" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="C82" s="1" t="n">
-        <v>1206</v>
+        <v>467</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>366</v>
+        <v>391</v>
       </c>
       <c r="G82" s="4" t="n">
         <f aca="false">SUM(H82:J82)</f>
@@ -5489,332 +5141,332 @@
       <c r="I82" s="4"/>
       <c r="J82" s="4"/>
       <c r="K82" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="L82" s="5"/>
+        <v>469</v>
+      </c>
+      <c r="L82" s="5" t="s">
+        <v>470</v>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>465</v>
+        <v>375</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>151</v>
+        <v>70</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>468</v>
+        <v>378</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>154</v>
+        <v>379</v>
       </c>
       <c r="G83" s="4" t="n">
         <f aca="false">SUM(H83:J83)</f>
-        <v>2</v>
+        <v>1000</v>
       </c>
       <c r="H83" s="4" t="n">
-        <v>2</v>
+        <v>1000</v>
       </c>
       <c r="I83" s="4"/>
       <c r="J83" s="4"/>
       <c r="K83" s="1" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="L83" s="5" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="8" t="s">
-        <v>465</v>
-      </c>
-      <c r="B84" s="8" t="s">
-        <v>471</v>
+      <c r="A84" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>475</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="D84" s="8" t="s">
-        <v>472</v>
-      </c>
-      <c r="E84" s="7" t="s">
-        <v>473</v>
-      </c>
-      <c r="F84" s="7" t="s">
-        <v>154</v>
+        <v>70</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>379</v>
       </c>
       <c r="G84" s="4" t="n">
         <f aca="false">SUM(H84:J84)</f>
-        <v>200</v>
-      </c>
-      <c r="H84" s="1" t="n">
-        <v>200</v>
-      </c>
-      <c r="K84" s="8" t="s">
-        <v>474</v>
-      </c>
-      <c r="L84" s="9" t="s">
-        <v>475</v>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="H84" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I84" s="4"/>
+      <c r="J84" s="4"/>
+      <c r="K84" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="L84" s="5"/>
     </row>
     <row r="85" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>151</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>154</v>
       </c>
       <c r="G85" s="4" t="n">
         <f aca="false">SUM(H85:J85)</f>
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="H85" s="4" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I85" s="4"/>
       <c r="J85" s="4"/>
       <c r="K85" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="L85" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="9" t="s">
         <v>478</v>
       </c>
-      <c r="L85" s="5" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>481</v>
+      <c r="B86" s="9" t="s">
+        <v>484</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="F86" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="D86" s="9" t="s">
         <v>485</v>
+      </c>
+      <c r="E86" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="F86" s="8" t="s">
+        <v>154</v>
       </c>
       <c r="G86" s="4" t="n">
         <f aca="false">SUM(H86:J86)</f>
-        <v>600</v>
-      </c>
-      <c r="H86" s="4" t="n">
-        <v>600</v>
-      </c>
-      <c r="I86" s="4"/>
-      <c r="J86" s="4"/>
-      <c r="K86" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="L86" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="H86" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="K86" s="9" t="s">
         <v>487</v>
+      </c>
+      <c r="L86" s="10" t="s">
+        <v>488</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>482</v>
+        <v>151</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>485</v>
+        <v>154</v>
       </c>
       <c r="G87" s="4" t="n">
         <f aca="false">SUM(H87:J87)</f>
-        <v>200</v>
+        <v>16</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>200</v>
+        <v>16</v>
       </c>
       <c r="I87" s="4"/>
       <c r="J87" s="4"/>
       <c r="K87" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L87" s="5" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G88" s="4" t="n">
         <f aca="false">SUM(H88:J88)</f>
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="I88" s="4"/>
       <c r="J88" s="4"/>
       <c r="K88" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L88" s="5" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G89" s="4" t="n">
         <f aca="false">SUM(H89:J89)</f>
-        <v>42</v>
+        <v>200</v>
       </c>
       <c r="H89" s="4" t="n">
-        <v>42</v>
+        <v>200</v>
       </c>
       <c r="I89" s="4"/>
       <c r="J89" s="4"/>
       <c r="K89" s="1" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="L89" s="5" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>151</v>
+        <v>507</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="G90" s="4" t="n">
         <f aca="false">SUM(H90:J90)</f>
-        <v>44</v>
+        <v>200</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>44</v>
+        <v>200</v>
       </c>
       <c r="I90" s="4"/>
       <c r="J90" s="4"/>
       <c r="K90" s="1" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="L90" s="5" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="F91" s="1" t="s">
         <v>510</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>485</v>
       </c>
       <c r="G91" s="4" t="n">
         <f aca="false">SUM(H91:J91)</f>
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="H91" s="4" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="I91" s="4"/>
       <c r="J91" s="4"/>
       <c r="K91" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="L91" s="5" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>517</v>
+        <v>151</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>518</v>
@@ -5827,10 +5479,10 @@
       </c>
       <c r="G92" s="4" t="n">
         <f aca="false">SUM(H92:J92)</f>
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="I92" s="4"/>
       <c r="J92" s="4"/>
@@ -5849,58 +5501,58 @@
         <v>524</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>273</v>
+        <v>495</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>525</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>526</v>
+        <v>168</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>527</v>
+        <v>498</v>
       </c>
       <c r="G93" s="4" t="n">
         <f aca="false">SUM(H93:J93)</f>
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H93" s="4" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="I93" s="4"/>
       <c r="J93" s="4"/>
       <c r="K93" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="L93" s="5" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C94" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="D94" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="E94" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="F94" s="1" t="s">
         <v>533</v>
-      </c>
-      <c r="E94" s="8" t="s">
-        <v>526</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>527</v>
       </c>
       <c r="G94" s="4" t="n">
         <f aca="false">SUM(H94:J94)</f>
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="I94" s="4"/>
       <c r="J94" s="4"/>
@@ -5913,57 +5565,57 @@
     </row>
     <row r="95" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>532</v>
+        <v>210</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>537</v>
-      </c>
-      <c r="E95" s="8" t="s">
         <v>538</v>
       </c>
+      <c r="E95" s="1" t="s">
+        <v>539</v>
+      </c>
       <c r="F95" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="G95" s="4" t="n">
         <f aca="false">SUM(H95:J95)</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H95" s="4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I95" s="4"/>
       <c r="J95" s="4"/>
       <c r="K95" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="L95" s="5" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>530</v>
+        <v>543</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>532</v>
+        <v>217</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>543</v>
-      </c>
-      <c r="E96" s="8" t="s">
-        <v>544</v>
+        <v>545</v>
+      </c>
+      <c r="E96" s="9" t="s">
+        <v>539</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="G96" s="4" t="n">
         <f aca="false">SUM(H96:J96)</f>
@@ -5983,22 +5635,22 @@
     </row>
     <row r="97" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="B97" s="1" t="n">
-        <v>555</v>
-      </c>
       <c r="C97" s="1" t="s">
-        <v>352</v>
+        <v>217</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E97" s="1" t="s">
+      <c r="E97" s="9" t="s">
         <v>550</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>154</v>
+        <v>551</v>
       </c>
       <c r="G97" s="4" t="n">
         <f aca="false">SUM(H97:J97)</f>
@@ -6010,223 +5662,225 @@
       <c r="I97" s="4"/>
       <c r="J97" s="4"/>
       <c r="K97" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="L97" s="5"/>
+        <v>552</v>
+      </c>
+      <c r="L97" s="5" t="s">
+        <v>553</v>
+      </c>
     </row>
     <row r="98" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="B98" s="8" t="s">
-        <v>553</v>
+        <v>543</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>554</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D98" s="8" t="s">
-        <v>554</v>
-      </c>
-      <c r="E98" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="D98" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="F98" s="7" t="s">
-        <v>313</v>
+      <c r="E98" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>557</v>
       </c>
       <c r="G98" s="4" t="n">
         <f aca="false">SUM(H98:J98)</f>
-        <v>2000</v>
-      </c>
-      <c r="H98" s="1" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K98" s="8" t="s">
-        <v>556</v>
-      </c>
-      <c r="L98" s="9" t="s">
-        <v>557</v>
+        <v>50</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="I98" s="4"/>
+      <c r="J98" s="4"/>
+      <c r="K98" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="L98" s="5" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="B99" s="8" t="s">
-        <v>558</v>
+        <v>560</v>
+      </c>
+      <c r="B99" s="1" t="n">
+        <v>555</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D99" s="8" t="s">
-        <v>559</v>
-      </c>
-      <c r="E99" s="7" t="s">
-        <v>560</v>
-      </c>
-      <c r="F99" s="7" t="s">
-        <v>313</v>
+        <v>365</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="G99" s="4" t="n">
         <f aca="false">SUM(H99:J99)</f>
-        <v>1000</v>
-      </c>
-      <c r="H99" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K99" s="8" t="s">
-        <v>561</v>
-      </c>
-      <c r="L99" s="9" t="s">
-        <v>562</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="H99" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="I99" s="4"/>
+      <c r="J99" s="4"/>
+      <c r="K99" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="L99" s="5"/>
     </row>
     <row r="100" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="B100" s="1" t="s">
         <v>564</v>
       </c>
+      <c r="B100" s="9" t="s">
+        <v>565</v>
+      </c>
       <c r="C100" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="D100" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D100" s="9" t="s">
         <v>566</v>
       </c>
-      <c r="E100" s="7" t="s">
+      <c r="E100" s="8" t="s">
         <v>567</v>
       </c>
-      <c r="F100" s="7" t="s">
-        <v>568</v>
+      <c r="F100" s="8" t="s">
+        <v>326</v>
       </c>
       <c r="G100" s="4" t="n">
         <f aca="false">SUM(H100:J100)</f>
-        <v>150</v>
-      </c>
-      <c r="H100" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="I100" s="4"/>
-      <c r="J100" s="4"/>
-      <c r="K100" s="1" t="s">
+        <v>2000</v>
+      </c>
+      <c r="H100" s="1" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K100" s="9" t="s">
+        <v>568</v>
+      </c>
+      <c r="L100" s="10" t="s">
         <v>569</v>
-      </c>
-      <c r="L100" s="5" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B101" s="9" t="s">
+        <v>570</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="D101" s="9" t="s">
         <v>571</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="E101" s="8" t="s">
         <v>572</v>
       </c>
-      <c r="C101" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>574</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>169</v>
+      <c r="F101" s="8" t="s">
+        <v>326</v>
       </c>
       <c r="G101" s="4" t="n">
         <f aca="false">SUM(H101:J101)</f>
-        <v>300</v>
-      </c>
-      <c r="H101" s="4" t="n">
-        <v>300</v>
-      </c>
-      <c r="I101" s="4"/>
-      <c r="J101" s="4"/>
-      <c r="K101" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="L101" s="5" t="s">
-        <v>577</v>
+        <v>1000</v>
+      </c>
+      <c r="H101" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K101" s="9" t="s">
+        <v>573</v>
+      </c>
+      <c r="L101" s="10" t="s">
+        <v>574</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="D102" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="E102" s="8" t="s">
         <v>579</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="F102" s="8" t="s">
         <v>580</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>581</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>583</v>
       </c>
       <c r="G102" s="4" t="n">
         <f aca="false">SUM(H102:J102)</f>
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="I102" s="4"/>
       <c r="J102" s="4"/>
       <c r="K102" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="L102" s="5"/>
+        <v>581</v>
+      </c>
+      <c r="L102" s="5" t="s">
+        <v>582</v>
+      </c>
     </row>
     <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="C103" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="D103" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="C103" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="D103" s="3" t="s">
+      <c r="E103" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="E103" s="1" t="s">
-        <v>588</v>
-      </c>
       <c r="F103" s="1" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="G103" s="4" t="n">
         <f aca="false">SUM(H103:J103)</f>
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H103" s="4" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I103" s="4"/>
       <c r="J103" s="4"/>
       <c r="K103" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="L103" s="5" t="s">
         <v>589</v>
-      </c>
-      <c r="L103" s="5" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="B104" s="1" t="s">
+      <c r="C104" s="1" t="s">
         <v>592</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>310</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>593</v>
@@ -6239,10 +5893,10 @@
       </c>
       <c r="G104" s="4" t="n">
         <f aca="false">SUM(H104:J104)</f>
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="H104" s="4" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="I104" s="4"/>
       <c r="J104" s="4"/>
@@ -6259,43 +5913,99 @@
         <v>598</v>
       </c>
       <c r="C105" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="D105" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="D105" s="3" t="s">
+      <c r="E105" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="E105" s="1" t="s">
-        <v>601</v>
-      </c>
       <c r="F105" s="1" t="s">
-        <v>602</v>
+        <v>177</v>
       </c>
       <c r="G105" s="4" t="n">
         <f aca="false">SUM(H105:J105)</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H105" s="4" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I105" s="4"/>
       <c r="J105" s="4"/>
       <c r="K105" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="L105" s="5" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="L105" s="5" t="s">
+      <c r="B106" s="1" t="s">
         <v>604</v>
       </c>
-    </row>
-    <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C106" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>607</v>
+      </c>
       <c r="G106" s="4" t="n">
         <f aca="false">SUM(H106:J106)</f>
-        <v>0</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="H106" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="I106" s="4"/>
+      <c r="J106" s="4"/>
+      <c r="K106" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="L106" s="5"/>
     </row>
     <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>614</v>
+      </c>
       <c r="G107" s="4" t="n">
         <f aca="false">SUM(H107:J107)</f>
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="H107" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="I107" s="4"/>
+      <c r="J107" s="4"/>
+      <c r="K107" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="L107" s="5" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6978,12 +6688,14 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="L37" r:id="rId1" display="https://www.lcsc.com/datasheet/C278365.pdf"/>
-    <hyperlink ref="L49" r:id="rId2" display="https://www.everlighteurope.com/custom/files/datasheets/DPC-0000031.pdf"/>
-    <hyperlink ref="L66" r:id="rId3" display="https://www.lcsc.com/datasheet/C4190.pdf"/>
-    <hyperlink ref="L84" r:id="rId4" display="https://www.lcsc.com/datasheet/C668205.pdf"/>
-    <hyperlink ref="L98" r:id="rId5" display="https://www.lcsc.com/datasheet/C20526.pdf"/>
-    <hyperlink ref="L99" r:id="rId6" display="https://www.lcsc.com/datasheet/C2143.pdf"/>
+    <hyperlink ref="L33" r:id="rId1" display="https://www.lcsc.com/datasheet/C541851.pdf"/>
+    <hyperlink ref="L34" r:id="rId2" display="https://www.lcsc.com/datasheet/C2691448.pdf"/>
+    <hyperlink ref="L40" r:id="rId3" display="https://www.lcsc.com/datasheet/C278365.pdf"/>
+    <hyperlink ref="L51" r:id="rId4" display="https://www.everlighteurope.com/custom/files/datasheets/DPC-0000031.pdf"/>
+    <hyperlink ref="L68" r:id="rId5" display="https://www.lcsc.com/datasheet/C4190.pdf"/>
+    <hyperlink ref="L86" r:id="rId6" display="https://www.lcsc.com/datasheet/C668205.pdf"/>
+    <hyperlink ref="L100" r:id="rId7" display="https://www.lcsc.com/datasheet/C20526.pdf"/>
+    <hyperlink ref="L101" r:id="rId8" display="https://www.lcsc.com/datasheet/C2143.pdf"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6993,1391 +6705,7 @@
     <oddFooter/>
   </headerFooter>
   <tableParts>
-    <tablePart r:id="rId7"/>
+    <tablePart r:id="rId9"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultColWidth="9.7578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="36.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="130.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="56.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="96.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="85.15"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
-        <v>605</v>
-      </c>
-      <c r="B1" s="10"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>606</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>608</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>610</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>612</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>616</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>618</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>620</v>
-      </c>
-      <c r="B9" s="1" t="n">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>621</v>
-      </c>
-      <c r="B10" s="1" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>622</v>
-      </c>
-      <c r="B11" s="1" t="n">
-        <v>2232</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>623</v>
-      </c>
-      <c r="B12" s="1" t="n">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="B13" s="1" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="B14" s="1" t="n">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>626</v>
-      </c>
-      <c r="B15" s="1" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>627</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>628</v>
-      </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>642</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>644</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>655</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B44" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="D44" s="11" t="s">
-        <v>662</v>
-      </c>
-      <c r="E44" s="11" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>669</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>669</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>669</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>669</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>674</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>669</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>674</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>669</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>669</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>669</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>674</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>689</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>689</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="s">
-        <v>696</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>669</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>689</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>702</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="C77" s="1" t="n">
-        <v>1206</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>702</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>702</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>702</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="C80" s="1" t="n">
-        <v>1206</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>702</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>702</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>702</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>702</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>702</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="C85" s="1" t="n">
-        <v>1206</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>702</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="B94" s="1" t="n">
-        <v>555</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>689</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>726</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
 </file>